--- a/pandemic-loss-modeling/exceedance_results/marani_inspired_outlier.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/marani_inspired_outlier.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -390,7 +390,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
         <v>0.1</v>
@@ -398,81 +398,73 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>0.002</v>
+        <v>7.2</v>
       </c>
       <c r="B3">
-        <v>0.1</v>
+        <v>0.03270749063847563</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>0.03270749063847563</v>
+        <v>0.0156127115217678</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B5">
-        <v>0.0156127115217678</v>
+        <v>0.0118776935903698</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="B6">
-        <v>0.0118776935903698</v>
+        <v>0.008130933190474199</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="B7">
-        <v>0.008130933190474199</v>
+        <v>0.005853629280596462</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="B8">
-        <v>0.005853629280596462</v>
+        <v>0.004935410919774863</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B9">
-        <v>0.004935410919774863</v>
+        <v>0.004663807298721389</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="B10">
-        <v>0.004663807298721389</v>
+        <v>0.004322629210627715</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="B11">
-        <v>0.004322629210627715</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>280</v>
-      </c>
-      <c r="B12">
         <v>0.004040922660135871</v>
       </c>
     </row>

--- a/pandemic-loss-modeling/exceedance_results/marani_inspired_outlier.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/marani_inspired_outlier.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -398,73 +398,249 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>7.2</v>
+        <v>0.04</v>
       </c>
       <c r="B3">
-        <v>0.03270749063847563</v>
+        <v>0.09865584415320848</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="B4">
-        <v>0.0156127115217678</v>
+        <v>0.09735892896685207</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>45</v>
+        <v>0.08</v>
       </c>
       <c r="B5">
-        <v>0.0118776935903698</v>
+        <v>0.09693665931805018</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>86</v>
+        <v>0.1</v>
       </c>
       <c r="B6">
-        <v>0.008130933190474199</v>
+        <v>0.09610661297096489</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>150</v>
+        <v>0.4</v>
       </c>
       <c r="B7">
-        <v>0.005853629280596462</v>
+        <v>0.08557726729797197</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>200</v>
+        <v>0.7</v>
       </c>
       <c r="B8">
-        <v>0.004935410919774863</v>
+        <v>0.07765621200777144</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="B9">
-        <v>0.004663807298721389</v>
+        <v>0.07143338391372719</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="B10">
-        <v>0.004322629210627715</v>
+        <v>0.04337494365927153</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>0.03317621032141908</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>0.03099581770860516</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>0.02758990118019592</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>0.02216508841976593</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>20</v>
+      </c>
+      <c r="B15">
+        <v>0.01889015813450237</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>28</v>
+      </c>
+      <c r="B16">
+        <v>0.0156127115217678</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>40</v>
+      </c>
+      <c r="B17">
+        <v>0.01271716529091473</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>45</v>
+      </c>
+      <c r="B18">
+        <v>0.0118776935903698</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>70</v>
+      </c>
+      <c r="B19">
+        <v>0.009176601444350996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>86</v>
+      </c>
+      <c r="B20">
+        <v>0.008130933190474199</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>100</v>
+      </c>
+      <c r="B21">
+        <v>0.007439436312336745</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>120</v>
+      </c>
+      <c r="B22">
+        <v>0.006680041065465237</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>150</v>
+      </c>
+      <c r="B23">
+        <v>0.005853629280596462</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>170</v>
+      </c>
+      <c r="B24">
+        <v>0.00543506863349289</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>190</v>
+      </c>
+      <c r="B25">
+        <v>0.00508799742542837</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>200</v>
+      </c>
+      <c r="B26">
+        <v>0.004935410919774863</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>220</v>
+      </c>
+      <c r="B27">
+        <v>0.004663807298721389</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>230</v>
+      </c>
+      <c r="B28">
+        <v>0.004542246114505144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>240</v>
+      </c>
+      <c r="B29">
+        <v>0.004428802077980865</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>250</v>
+      </c>
+      <c r="B30">
+        <v>0.004322629210627715</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>260</v>
+      </c>
+      <c r="B31">
+        <v>0.004222998940997514</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>270</v>
+      </c>
+      <c r="B32">
+        <v>0.004129280054008089</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
         <v>280</v>
       </c>
-      <c r="B11">
+      <c r="B33">
         <v>0.004040922660135871</v>
       </c>
     </row>
